--- a/Ladies Singles Medals Wiki.xlsx
+++ b/Ladies Singles Medals Wiki.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11113"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulinareina/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulinareina/Desktop/Career Exploration Stuff/Data Science Training/The Data Incubator/The Data Incubator Onboarding/Streamlit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DF91712-0FF1-3A48-A9F7-28B63C3B4D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D27D4C-4C16-A14E-ABF6-E7CF424F8F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16300" xr2:uid="{B25230AE-A172-F849-889C-0791388BB18D}"/>
+    <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16300" xr2:uid="{B25230AE-A172-F849-889C-0791388BB18D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="123">
   <si>
     <t>Games</t>
   </si>
@@ -389,6 +388,21 @@
   </si>
   <si>
     <t>Kaori Sakamoto</t>
+  </si>
+  <si>
+    <t>2026 Milano Cortina</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>Ami Nakai</t>
+  </si>
+  <si>
+    <t>Alysa Liu</t>
   </si>
 </sst>
 </file>
@@ -5465,7 +5479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4154E2D2-DDCE-9245-95B1-C3C37593826C}">
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.2">
@@ -6216,6 +6230,34 @@
       </c>
       <c r="D54" s="2" t="s">
         <v>82</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>118</v>
+      </c>
+      <c r="B55" t="s">
+        <v>122</v>
+      </c>
+      <c r="C55" t="s">
+        <v>117</v>
+      </c>
+      <c r="D55" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56" t="s">
+        <v>119</v>
+      </c>
+      <c r="C56" t="s">
+        <v>120</v>
+      </c>
+      <c r="D56" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
